--- a/DECK.xlsx
+++ b/DECK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B5D0AB-A70E-421A-8BA2-3279C69CFE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45EE06DD-7B76-4ECE-98C5-27509F02853B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{32EF9E8E-5778-4FD9-8E72-014E2CEE3192}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{32EF9E8E-5778-4FD9-8E72-014E2CEE3192}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="110">
   <si>
     <t>DECK</t>
   </si>
@@ -355,6 +355,18 @@
   </si>
   <si>
     <t>n.a.</t>
+  </si>
+  <si>
+    <t>Q127</t>
+  </si>
+  <si>
+    <t>Q227</t>
+  </si>
+  <si>
+    <t>Q327</t>
+  </si>
+  <si>
+    <t>Q427</t>
   </si>
 </sst>
 </file>
@@ -367,13 +379,19 @@
     <numFmt numFmtId="166" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="167" formatCode="#,##0.00;[Red]#,##0.00"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -530,46 +548,50 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -930,7 +952,7 @@
         <v>3</v>
       </c>
       <c r="M2" s="3">
-        <v>107</v>
+        <v>103.91</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
@@ -940,11 +962,11 @@
       <c r="L3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="5">
-        <v>138.880957</v>
-      </c>
-      <c r="N3" s="26" t="s">
-        <v>103</v>
+      <c r="M3" s="3">
+        <v>138.26300000000001</v>
+      </c>
+      <c r="N3" s="28" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -962,7 +984,7 @@
       </c>
       <c r="M4" s="5">
         <f>M3*M2</f>
-        <v>14860.262398999999</v>
+        <v>14366.90833</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -976,10 +998,10 @@
         <v>6</v>
       </c>
       <c r="M5" s="5">
-        <v>1907.249</v>
-      </c>
-      <c r="N5" s="26" t="s">
-        <v>103</v>
+        <v>1602.5889999999999</v>
+      </c>
+      <c r="N5" s="28" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -989,8 +1011,8 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-      <c r="N6" s="26" t="s">
-        <v>103</v>
+      <c r="N6" s="28" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -1002,7 +1024,7 @@
       </c>
       <c r="M7" s="5">
         <f>M4-M5+M6</f>
-        <v>12953.013398999999</v>
+        <v>12764.31933</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -1108,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E627EB27-452B-48DD-8092-5ECA5113EA18}">
-  <dimension ref="A1:W67"/>
+  <dimension ref="A1:AA67"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="2" customWidth="1"/>
@@ -1116,12 +1138,12 @@
     <col min="3" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
         <v>11</v>
       </c>
@@ -1158,32 +1180,44 @@
       <c r="N2" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="O2" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="P2" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q2" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="R2" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="T2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="U2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="V2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="W2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="X2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="Y2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="Z2" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="W2" s="26" t="s">
+      <c r="AA2" s="26" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="18"/>
       <c r="B3" s="3" t="s">
         <v>25</v>
@@ -1197,20 +1231,20 @@
       <c r="M3" s="19">
         <v>1305.4749999999999</v>
       </c>
-      <c r="T3" s="19">
+      <c r="X3" s="19">
         <v>1929.211</v>
       </c>
-      <c r="U3" s="19">
+      <c r="Y3" s="19">
         <v>2239.1320000000001</v>
       </c>
-      <c r="V3" s="20">
+      <c r="Z3" s="20">
         <v>2531.3510000000001</v>
       </c>
-      <c r="W3" s="19">
+      <c r="AA3" s="19">
         <v>2738.7579999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="18"/>
       <c r="B4" s="3" t="s">
         <v>26</v>
@@ -1224,20 +1258,20 @@
       <c r="M4" s="19">
         <v>628.88199999999995</v>
       </c>
-      <c r="T4" s="19">
+      <c r="X4" s="19">
         <v>1412.9159999999999</v>
       </c>
-      <c r="U4" s="19">
+      <c r="Y4" s="19">
         <v>1806.74</v>
       </c>
-      <c r="V4" s="20">
+      <c r="Z4" s="20">
         <v>2233.09</v>
       </c>
-      <c r="W4" s="19">
+      <c r="AA4" s="19">
         <v>2587.33</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="18"/>
       <c r="B5" s="3" t="s">
         <v>27</v>
@@ -1251,20 +1285,20 @@
       <c r="M5" s="19">
         <v>0</v>
       </c>
-      <c r="T5" s="19">
+      <c r="X5" s="19">
         <v>183.06100000000001</v>
       </c>
-      <c r="U5" s="19">
+      <c r="Y5" s="19">
         <v>148.51900000000001</v>
       </c>
-      <c r="V5" s="27" t="s">
+      <c r="Z5" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="W5" s="27" t="s">
+      <c r="AA5" s="27" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="18"/>
       <c r="B6" s="3" t="s">
         <v>28</v>
@@ -1278,20 +1312,20 @@
       <c r="M6" s="19">
         <v>0</v>
       </c>
-      <c r="T6" s="19">
+      <c r="X6" s="19">
         <v>37.966000000000001</v>
       </c>
-      <c r="U6" s="19">
+      <c r="Y6" s="19">
         <v>25.449000000000002</v>
       </c>
-      <c r="V6" s="27" t="s">
+      <c r="Z6" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="W6" s="27" t="s">
+      <c r="AA6" s="27" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="18"/>
       <c r="B7" s="3" t="s">
         <v>29</v>
@@ -1305,20 +1339,20 @@
       <c r="M7" s="19">
         <v>23.192</v>
       </c>
-      <c r="T7" s="19">
+      <c r="X7" s="19">
         <v>64.132000000000005</v>
       </c>
-      <c r="U7" s="19">
+      <c r="Y7" s="19">
         <v>67.923000000000002</v>
       </c>
-      <c r="V7" s="20">
+      <c r="Z7" s="20">
         <v>175.77</v>
       </c>
-      <c r="W7" s="19">
+      <c r="AA7" s="19">
         <v>146.208</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="18"/>
       <c r="B8" s="3" t="s">
         <v>99</v>
@@ -1326,14 +1360,14 @@
       <c r="M8" s="19">
         <v>864.57</v>
       </c>
-      <c r="V8" s="20">
+      <c r="Z8" s="20">
         <v>2855.8649999999998</v>
       </c>
-      <c r="W8" s="19">
+      <c r="AA8" s="19">
         <v>3208.107</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="18"/>
       <c r="B9" s="3" t="s">
         <v>94</v>
@@ -1347,14 +1381,14 @@
       <c r="M9" s="19">
         <v>1092.979</v>
       </c>
-      <c r="V9" s="20">
+      <c r="Z9" s="20">
         <v>2129.7469999999998</v>
       </c>
-      <c r="W9" s="19">
+      <c r="AA9" s="19">
         <v>2264.1889999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B10" s="21" t="s">
         <v>20</v>
       </c>
@@ -1386,27 +1420,33 @@
         <v>1957.549</v>
       </c>
       <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
+      <c r="O10" s="22">
+        <v>1019.5309999999999</v>
+      </c>
       <c r="P10" s="22"/>
       <c r="Q10" s="22"/>
       <c r="R10" s="22"/>
-      <c r="S10" s="22">
+      <c r="S10" s="22"/>
+      <c r="T10" s="22"/>
+      <c r="U10" s="22"/>
+      <c r="V10" s="22"/>
+      <c r="W10" s="22">
         <v>3150.3389999999999</v>
       </c>
-      <c r="T10" s="22">
+      <c r="X10" s="22">
         <v>3627.2860000000001</v>
       </c>
-      <c r="U10" s="22">
+      <c r="Y10" s="22">
         <v>4287.7629999999999</v>
       </c>
-      <c r="V10" s="22">
+      <c r="Z10" s="22">
         <v>4985.6120000000001</v>
       </c>
-      <c r="W10" s="22">
+      <c r="AA10" s="22">
         <v>5472.2960000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
@@ -1434,28 +1474,31 @@
       <c r="M11" s="19">
         <v>786.18899999999996</v>
       </c>
-      <c r="S11" s="19">
+      <c r="O11" s="19">
+        <v>444.36799999999999</v>
+      </c>
+      <c r="W11" s="19">
         <v>1542.788</v>
       </c>
-      <c r="T11" s="19">
+      <c r="X11" s="19">
         <v>1801.9159999999999</v>
       </c>
-      <c r="U11" s="19">
+      <c r="Y11" s="19">
         <v>1902.2750000000001</v>
       </c>
-      <c r="V11" s="19">
+      <c r="Z11" s="19">
         <v>2099.9490000000001</v>
       </c>
-      <c r="W11" s="19">
+      <c r="AA11" s="19">
         <v>2314.5700000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="19">
-        <f t="shared" ref="C12:M12" si="0">C10-C11</f>
+        <f t="shared" ref="C12:O12" si="0">C10-C11</f>
         <v>0</v>
       </c>
       <c r="D12" s="19">
@@ -1498,40 +1541,48 @@
         <f t="shared" si="0"/>
         <v>1171.3600000000001</v>
       </c>
-      <c r="P12" s="19">
-        <f t="shared" ref="P12:T12" si="1">P10-P11</f>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="19">
+      <c r="N12" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O12" s="19">
+        <f t="shared" si="0"/>
+        <v>575.16300000000001</v>
+      </c>
+      <c r="T12" s="19">
+        <f t="shared" ref="T12:X12" si="1">T10-T11</f>
+        <v>0</v>
+      </c>
+      <c r="U12" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R12" s="19">
+      <c r="V12" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S12" s="19">
+      <c r="W12" s="19">
         <f t="shared" si="1"/>
         <v>1607.5509999999999</v>
       </c>
-      <c r="T12" s="19">
+      <c r="X12" s="19">
         <f t="shared" si="1"/>
         <v>1825.3700000000001</v>
       </c>
-      <c r="U12" s="19">
-        <f>U10-U11</f>
+      <c r="Y12" s="19">
+        <f>Y10-Y11</f>
         <v>2385.4879999999998</v>
       </c>
-      <c r="V12" s="19">
-        <f>V10-V11</f>
+      <c r="Z12" s="19">
+        <f>Z10-Z11</f>
         <v>2885.663</v>
       </c>
-      <c r="W12" s="19">
-        <f>W10-W11</f>
+      <c r="AA12" s="19">
+        <f>AA10-AA11</f>
         <v>3157.7260000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>23</v>
       </c>
@@ -1559,23 +1610,26 @@
       <c r="M13" s="19">
         <v>556.99400000000003</v>
       </c>
-      <c r="S13" s="19">
+      <c r="O13" s="19">
+        <v>419.86200000000002</v>
+      </c>
+      <c r="W13" s="19">
         <v>1042.8440000000001</v>
       </c>
-      <c r="T13" s="19">
+      <c r="X13" s="19">
         <v>1172.6189999999999</v>
       </c>
-      <c r="U13" s="19">
+      <c r="Y13" s="19">
         <v>1457.9469999999999</v>
       </c>
-      <c r="V13" s="19">
+      <c r="Z13" s="19">
         <v>1706.5709999999999</v>
       </c>
-      <c r="W13" s="19">
+      <c r="AA13" s="19">
         <v>1894.8230000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>24</v>
       </c>
@@ -1592,7 +1646,7 @@
         <v>487.89899999999994</v>
       </c>
       <c r="F14" s="19">
-        <f t="shared" ref="F14:M14" si="5">F12-F13</f>
+        <f t="shared" ref="F14:O14" si="5">F12-F13</f>
         <v>0</v>
       </c>
       <c r="G14" s="19">
@@ -1623,40 +1677,48 @@
         <f t="shared" si="5"/>
         <v>614.3660000000001</v>
       </c>
-      <c r="P14" s="19">
-        <f t="shared" ref="P14:T14" si="6">P12-P13</f>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="19">
+      <c r="N14" s="19">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="19">
+        <f t="shared" si="5"/>
+        <v>155.30099999999999</v>
+      </c>
+      <c r="T14" s="19">
+        <f t="shared" ref="T14:X14" si="6">T12-T13</f>
+        <v>0</v>
+      </c>
+      <c r="U14" s="19">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R14" s="19">
+      <c r="V14" s="19">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S14" s="19">
+      <c r="W14" s="19">
         <f t="shared" si="6"/>
         <v>564.70699999999988</v>
       </c>
-      <c r="T14" s="19">
+      <c r="X14" s="19">
         <f t="shared" si="6"/>
         <v>652.7510000000002</v>
       </c>
-      <c r="U14" s="19">
-        <f>U12-U13</f>
+      <c r="Y14" s="19">
+        <f>Y12-Y13</f>
         <v>927.54099999999994</v>
       </c>
-      <c r="V14" s="19">
-        <f>V12-V13</f>
+      <c r="Z14" s="19">
+        <f>Z12-Z13</f>
         <v>1179.0920000000001</v>
       </c>
-      <c r="W14" s="19">
-        <f>W12-W13</f>
+      <c r="AA14" s="19">
+        <f>AA12-AA13</f>
         <v>1262.903</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>55</v>
       </c>
@@ -1684,23 +1746,26 @@
       <c r="M15" s="19">
         <v>13.523</v>
       </c>
-      <c r="S15" s="19">
+      <c r="O15" s="29">
+        <v>13.749000000000001</v>
+      </c>
+      <c r="W15" s="19">
         <v>1.901</v>
       </c>
-      <c r="T15" s="19">
+      <c r="X15" s="19">
         <v>15.563000000000001</v>
       </c>
-      <c r="U15" s="19">
+      <c r="Y15" s="19">
         <v>52.207999999999998</v>
       </c>
-      <c r="V15" s="19">
+      <c r="Z15" s="19">
         <v>68.388999999999996</v>
       </c>
-      <c r="W15" s="19">
+      <c r="AA15" s="19">
         <v>63.613</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>56</v>
       </c>
@@ -1728,23 +1793,26 @@
       <c r="M16" s="19">
         <v>1.069</v>
       </c>
-      <c r="S16" s="19">
+      <c r="O16" s="19">
+        <v>0</v>
+      </c>
+      <c r="W16" s="19">
         <v>2.0830000000000002</v>
       </c>
-      <c r="T16" s="19">
+      <c r="X16" s="19">
         <v>3.4420000000000002</v>
       </c>
-      <c r="U16" s="19">
+      <c r="Y16" s="19">
         <v>2.6539999999999999</v>
       </c>
-      <c r="V16" s="19">
+      <c r="Z16" s="19">
         <v>3.5169999999999999</v>
       </c>
-      <c r="W16" s="19">
+      <c r="AA16" s="19">
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>57</v>
       </c>
@@ -1772,23 +1840,26 @@
       <c r="M17" s="19">
         <v>9.0999999999999998E-2</v>
       </c>
-      <c r="S17" s="19">
+      <c r="O17" s="19">
+        <v>0</v>
+      </c>
+      <c r="W17" s="19">
         <v>0.113</v>
       </c>
-      <c r="T17" s="19">
+      <c r="X17" s="19">
         <v>1.21</v>
       </c>
-      <c r="U17" s="19">
+      <c r="Y17" s="19">
         <v>1.7829999999999999</v>
       </c>
-      <c r="V17" s="19">
+      <c r="Z17" s="19">
         <v>-0.66500000000000004</v>
       </c>
-      <c r="W17" s="19">
+      <c r="AA17" s="19">
         <v>2.37</v>
       </c>
     </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>58</v>
       </c>
@@ -1817,7 +1888,7 @@
         <v>318.91199999999998</v>
       </c>
       <c r="I18" s="19">
-        <f t="shared" ref="I18:M18" si="8">+I14-I16+I15+I17</f>
+        <f t="shared" ref="I18:O18" si="8">+I14-I16+I15+I17</f>
         <v>583.94200000000001</v>
       </c>
       <c r="J18" s="19">
@@ -1836,40 +1907,48 @@
         <f t="shared" si="8"/>
         <v>626.91100000000017</v>
       </c>
-      <c r="P18" s="19">
-        <f t="shared" ref="P18" si="9">+P14-P16+P15+P17</f>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="19">
-        <f t="shared" ref="Q18" si="10">+Q14-Q16+Q15+Q17</f>
-        <v>0</v>
-      </c>
-      <c r="R18" s="19">
-        <f t="shared" ref="R18" si="11">+R14-R16+R15+R17</f>
-        <v>0</v>
-      </c>
-      <c r="S18" s="19">
-        <f t="shared" ref="S18" si="12">+S14-S16+S15+S17</f>
+      <c r="N18" s="19">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="19">
+        <f t="shared" si="8"/>
+        <v>169.04999999999998</v>
+      </c>
+      <c r="T18" s="19">
+        <f t="shared" ref="T18" si="9">+T14-T16+T15+T17</f>
+        <v>0</v>
+      </c>
+      <c r="U18" s="19">
+        <f t="shared" ref="U18" si="10">+U14-U16+U15+U17</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="19">
+        <f t="shared" ref="V18" si="11">+V14-V16+V15+V17</f>
+        <v>0</v>
+      </c>
+      <c r="W18" s="19">
+        <f t="shared" ref="W18" si="12">+W14-W16+W15+W17</f>
         <v>564.63799999999992</v>
       </c>
-      <c r="T18" s="19">
-        <f t="shared" ref="T18" si="13">+T14-T16+T15+T17</f>
+      <c r="X18" s="19">
+        <f t="shared" ref="X18" si="13">+X14-X16+X15+X17</f>
         <v>666.08200000000022</v>
       </c>
-      <c r="U18" s="19">
-        <f t="shared" ref="U18:W18" si="14">+U14-U16+U15+U17</f>
+      <c r="Y18" s="19">
+        <f t="shared" ref="Y18:AA18" si="14">+Y14-Y16+Y15+Y17</f>
         <v>978.87799999999993</v>
       </c>
-      <c r="V18" s="19">
+      <c r="Z18" s="19">
         <f t="shared" si="14"/>
         <v>1243.299</v>
       </c>
-      <c r="W18" s="19">
+      <c r="AA18" s="19">
         <f t="shared" si="14"/>
         <v>1326.356</v>
       </c>
     </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>59</v>
       </c>
@@ -1897,23 +1976,27 @@
       <c r="M19" s="19">
         <v>145.768</v>
       </c>
-      <c r="S19" s="19">
+      <c r="O19" s="19">
+        <f>39.078-3.287</f>
+        <v>35.791000000000004</v>
+      </c>
+      <c r="W19" s="19">
         <v>112.68899999999999</v>
       </c>
-      <c r="T19" s="19">
+      <c r="X19" s="19">
         <v>149.26</v>
       </c>
-      <c r="U19" s="19">
+      <c r="Y19" s="19">
         <v>219.37799999999999</v>
       </c>
-      <c r="V19" s="19">
+      <c r="Z19" s="19">
         <v>277.20800000000003</v>
       </c>
-      <c r="W19" s="19">
+      <c r="AA19" s="19">
         <v>302.28500000000003</v>
       </c>
     </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
         <v>60</v>
       </c>
@@ -1962,47 +2045,47 @@
         <v>481.14300000000014</v>
       </c>
       <c r="N20" s="19">
-        <f t="shared" ref="N20:W20" si="16">+N18-N19</f>
+        <f t="shared" ref="N20:AA20" si="16">+N18-N19</f>
         <v>0</v>
       </c>
       <c r="O20" s="19">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="19">
+        <v>133.25899999999999</v>
+      </c>
+      <c r="T20" s="19">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="19">
+      <c r="U20" s="19">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="R20" s="19">
+      <c r="V20" s="19">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="S20" s="19">
+      <c r="W20" s="19">
         <f t="shared" si="16"/>
         <v>451.94899999999996</v>
       </c>
-      <c r="T20" s="19">
+      <c r="X20" s="19">
         <f t="shared" si="16"/>
         <v>516.82200000000023</v>
       </c>
-      <c r="U20" s="19">
+      <c r="Y20" s="19">
         <f t="shared" si="16"/>
         <v>759.5</v>
       </c>
-      <c r="V20" s="19">
+      <c r="Z20" s="19">
         <f t="shared" si="16"/>
         <v>966.09099999999989</v>
       </c>
-      <c r="W20" s="19">
+      <c r="AA20" s="19">
         <f t="shared" si="16"/>
         <v>1024.0709999999999</v>
       </c>
     </row>
-    <row r="21" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -2022,8 +2105,12 @@
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
-    </row>
-    <row r="22" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="3"/>
+      <c r="Y21" s="3"/>
+    </row>
+    <row r="22" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>61</v>
       </c>
@@ -2052,7 +2139,7 @@
         <v>1.5917038885969519</v>
       </c>
       <c r="I22" s="23">
-        <f t="shared" ref="I22:M22" si="18">+I20/I23</f>
+        <f t="shared" ref="I22:O22" si="18">+I20/I23</f>
         <v>3.0083915162692665</v>
       </c>
       <c r="J22" s="23" t="e">
@@ -2071,30 +2158,40 @@
         <f t="shared" si="18"/>
         <v>3.3396473936280988</v>
       </c>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
+      <c r="N22" s="23" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O22" s="23">
+        <f t="shared" si="18"/>
+        <v>0.96380810484366741</v>
+      </c>
       <c r="P22" s="23"/>
       <c r="Q22" s="23"/>
       <c r="R22" s="23"/>
-      <c r="S22" s="23">
+      <c r="S22" s="23"/>
+      <c r="T22" s="23"/>
+      <c r="U22" s="23"/>
+      <c r="V22" s="23"/>
+      <c r="W22" s="23">
         <v>16.43</v>
       </c>
-      <c r="T22" s="23">
+      <c r="X22" s="23">
         <v>19.5</v>
       </c>
-      <c r="U22" s="23">
+      <c r="Y22" s="23">
         <v>29.6</v>
       </c>
-      <c r="V22" s="23">
-        <f>+V20/V23</f>
+      <c r="Z22" s="23">
+        <f>+Z20/Z23</f>
         <v>6.3561963787567768</v>
       </c>
-      <c r="W22" s="23">
-        <f>+W20/W23</f>
+      <c r="AA22" s="23">
+        <f>+AA20/AA23</f>
         <v>7.0383854073595513</v>
       </c>
     </row>
-    <row r="23" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>62</v>
       </c>
@@ -2126,39 +2223,45 @@
         <v>144.07</v>
       </c>
       <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3" t="e">
-        <f t="shared" ref="P23:T23" si="19">P20/P22</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q23" s="3" t="e">
+      <c r="O23" s="3">
+        <v>138.26300000000001</v>
+      </c>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3" t="e">
+        <f t="shared" ref="T23:X23" si="19">T20/T22</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U23" s="3" t="e">
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R23" s="3" t="e">
+      <c r="V23" s="3" t="e">
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S23" s="3">
+      <c r="W23" s="3">
         <f t="shared" si="19"/>
         <v>27.507547169811318</v>
       </c>
-      <c r="T23" s="3">
+      <c r="X23" s="3">
         <f t="shared" si="19"/>
         <v>26.503692307692319</v>
       </c>
-      <c r="U23" s="3">
-        <f>U20/U22</f>
+      <c r="Y23" s="3">
+        <f>Y20/Y22</f>
         <v>25.658783783783782</v>
       </c>
-      <c r="V23" s="2">
+      <c r="Z23" s="2">
         <v>151.99199999999999</v>
       </c>
-      <c r="W23" s="2">
+      <c r="AA23" s="2">
         <v>145.49799999999999</v>
       </c>
     </row>
-    <row r="24" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -2178,8 +2281,12 @@
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
-    </row>
-    <row r="25" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+    </row>
+    <row r="25" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="3" t="s">
         <v>48</v>
       </c>
@@ -2188,63 +2295,67 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="24" t="e">
-        <f>+G3/C3-1</f>
+        <f t="shared" ref="G25:L26" si="20">+G3/C3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H25" s="24">
-        <f>+H3/D3-1</f>
+        <f t="shared" si="20"/>
         <v>0.13402944841216247</v>
       </c>
       <c r="I25" s="24" t="e">
-        <f>+I3/E3-1</f>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J25" s="24" t="e">
-        <f>+J3/F3-1</f>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K25" s="24" t="e">
-        <f>+K3/G3-1</f>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L25" s="24">
-        <f>+L3/H3-1</f>
+        <f t="shared" si="20"/>
         <v>-1</v>
       </c>
       <c r="M25" s="24"/>
       <c r="N25" s="24"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="24" t="e">
-        <f>Q3/P3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R25" s="24" t="e">
-        <f>R3/Q3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S25" s="24" t="e">
-        <f>S3/R3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T25" s="24" t="e">
-        <f>T3/S3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U25" s="24">
-        <f>U3/T3-1</f>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="24" t="e">
+        <f t="shared" ref="U25:AA26" si="21">U3/T3-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V25" s="24" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W25" s="24" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X25" s="24" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y25" s="24">
+        <f t="shared" si="21"/>
         <v>0.16064650263760671</v>
       </c>
-      <c r="V25" s="24">
-        <f>V3/U3-1</f>
+      <c r="Z25" s="24">
+        <f t="shared" si="21"/>
         <v>0.13050548158840125</v>
       </c>
-      <c r="W25" s="24">
-        <f>W3/V3-1</f>
+      <c r="AA25" s="24">
+        <f t="shared" si="21"/>
         <v>8.1935298581666371E-2</v>
       </c>
     </row>
-    <row r="26" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="3" t="s">
         <v>49</v>
       </c>
@@ -2253,63 +2364,67 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="24" t="e">
-        <f>+G4/C4-1</f>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H26" s="24">
-        <f>+H4/D4-1</f>
+        <f t="shared" si="20"/>
         <v>0.37787529518239515</v>
       </c>
       <c r="I26" s="24" t="e">
-        <f>+I4/E4-1</f>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J26" s="24" t="e">
-        <f>+J4/F4-1</f>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K26" s="24" t="e">
-        <f>+K4/G4-1</f>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L26" s="24">
-        <f>+L4/H4-1</f>
+        <f t="shared" si="20"/>
         <v>-1</v>
       </c>
       <c r="M26" s="24"/>
       <c r="N26" s="24"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="24" t="e">
-        <f>Q4/P4-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R26" s="24" t="e">
-        <f>R4/Q4-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S26" s="24" t="e">
-        <f>S4/R4-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T26" s="24" t="e">
-        <f>T4/S4-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U26" s="24">
-        <f>U4/T4-1</f>
+      <c r="O26" s="24"/>
+      <c r="P26" s="24"/>
+      <c r="Q26" s="24"/>
+      <c r="R26" s="24"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="24" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V26" s="24" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W26" s="24" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X26" s="24" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y26" s="24">
+        <f t="shared" si="21"/>
         <v>0.27873136124157427</v>
       </c>
-      <c r="V26" s="24">
-        <f>V4/U4-1</f>
+      <c r="Z26" s="24">
+        <f t="shared" si="21"/>
         <v>0.2359775064480778</v>
       </c>
-      <c r="W26" s="24">
-        <f>W4/V4-1</f>
+      <c r="AA26" s="24">
+        <f t="shared" si="21"/>
         <v>0.15863220918100018</v>
       </c>
     </row>
-    <row r="27" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="21" t="s">
         <v>50</v>
       </c>
@@ -2318,383 +2433,403 @@
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
       <c r="G27" s="25" t="e">
-        <f>+G10/C10-1</f>
+        <f t="shared" ref="G27:L27" si="22">+G10/C10-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H27" s="25">
-        <f>+H10/D10-1</f>
+        <f t="shared" si="22"/>
         <v>0.20094476910579373</v>
       </c>
       <c r="I27" s="25">
-        <f>+I10/E10-1</f>
+        <f t="shared" si="22"/>
         <v>0.17102916285064418</v>
       </c>
       <c r="J27" s="25" t="e">
-        <f>+J10/F10-1</f>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K27" s="25">
-        <f>+K10/G10-1</f>
+        <f t="shared" si="22"/>
         <v>0.16864543034626656</v>
       </c>
       <c r="L27" s="25">
-        <f>+L10/H10-1</f>
+        <f t="shared" si="22"/>
         <v>9.1144800658877978E-2</v>
       </c>
       <c r="M27" s="25"/>
       <c r="N27" s="25"/>
-      <c r="O27" s="21"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="25" t="e">
-        <f>Q10/P10-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R27" s="25" t="e">
-        <f>R10/Q10-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S27" s="25" t="e">
-        <f>S10/R10-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T27" s="25">
-        <f>T10/S10-1</f>
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="21"/>
+      <c r="T27" s="21"/>
+      <c r="U27" s="25" t="e">
+        <f t="shared" ref="U27:AA27" si="23">U10/T10-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V27" s="25" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W27" s="25" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X27" s="25">
+        <f t="shared" si="23"/>
         <v>0.15139545299728074</v>
       </c>
-      <c r="U27" s="25">
-        <f>U10/T10-1</f>
+      <c r="Y27" s="25">
+        <f t="shared" si="23"/>
         <v>0.18208572469885187</v>
       </c>
-      <c r="V27" s="25">
-        <f>V10/U10-1</f>
+      <c r="Z27" s="25">
+        <f t="shared" si="23"/>
         <v>0.16275363167227308</v>
       </c>
-      <c r="W27" s="25">
-        <f>W10/V10-1</f>
+      <c r="AA27" s="25">
+        <f t="shared" si="23"/>
         <v>9.7617704707064989E-2</v>
       </c>
     </row>
-    <row r="28" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C28" s="24" t="e">
-        <f>C12/C10</f>
+        <f t="shared" ref="C28:L28" si="24">C12/C10</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="24">
-        <f>D12/D10</f>
+        <f t="shared" si="24"/>
         <v>0.53394565654400972</v>
       </c>
       <c r="E28" s="24">
-        <f>E12/E10</f>
+        <f t="shared" si="24"/>
         <v>0.58742862782772876</v>
       </c>
       <c r="F28" s="24" t="e">
-        <f>F12/F10</f>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G28" s="24">
-        <f>G12/G10</f>
+        <f t="shared" si="24"/>
         <v>0.56945745244121559</v>
       </c>
       <c r="H28" s="24">
-        <f>H12/H10</f>
+        <f t="shared" si="24"/>
         <v>0.55918616356038187</v>
       </c>
       <c r="I28" s="24">
-        <f>I12/I10</f>
+        <f t="shared" si="24"/>
         <v>0.60346109957228822</v>
       </c>
       <c r="J28" s="24" t="e">
-        <f>J12/J10</f>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K28" s="24">
-        <f>K12/K10</f>
+        <f t="shared" si="24"/>
         <v>0.55768253816853242</v>
       </c>
       <c r="L28" s="24">
-        <f>L12/L10</f>
+        <f t="shared" si="24"/>
         <v>0.56178328813843614</v>
       </c>
       <c r="M28" s="24"/>
       <c r="N28" s="24"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="24" t="e">
-        <f>P12/P10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q28" s="24" t="e">
-        <f>Q12/Q10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R28" s="24" t="e">
-        <f>R12/R10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S28" s="24">
-        <f>S12/S10</f>
+      <c r="O28" s="24"/>
+      <c r="P28" s="24"/>
+      <c r="Q28" s="24"/>
+      <c r="R28" s="24"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="24" t="e">
+        <f t="shared" ref="T28:AA28" si="25">T12/T10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U28" s="24" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V28" s="24" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W28" s="24">
+        <f t="shared" si="25"/>
         <v>0.51027873508216104</v>
       </c>
-      <c r="T28" s="24">
-        <f>T12/T10</f>
+      <c r="X28" s="24">
+        <f t="shared" si="25"/>
         <v>0.50323299568878777</v>
       </c>
-      <c r="U28" s="24">
-        <f>U12/U10</f>
+      <c r="Y28" s="24">
+        <f t="shared" si="25"/>
         <v>0.55634791381893067</v>
       </c>
-      <c r="V28" s="24">
-        <f>V12/V10</f>
+      <c r="Z28" s="24">
+        <f t="shared" si="25"/>
         <v>0.57879814955515996</v>
       </c>
-      <c r="W28" s="24">
-        <f>W12/W10</f>
+      <c r="AA28" s="24">
+        <f t="shared" si="25"/>
         <v>0.57703859586542827</v>
       </c>
     </row>
-    <row r="29" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="3" t="s">
         <v>52</v>
       </c>
       <c r="C29" s="24" t="e">
-        <f>C14/C10</f>
+        <f t="shared" ref="C29:L29" si="26">C14/C10</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D29" s="24">
-        <f>D14/D10</f>
+        <f t="shared" si="26"/>
         <v>0.20571074276472268</v>
       </c>
       <c r="E29" s="24">
-        <f>E14/E10</f>
+        <f t="shared" si="26"/>
         <v>0.31269423260935186</v>
       </c>
       <c r="F29" s="24" t="e">
-        <f>F14/F10</f>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G29" s="24">
-        <f>G14/G10</f>
+        <f t="shared" si="26"/>
         <v>0.16091050188587347</v>
       </c>
       <c r="H29" s="24">
-        <f>H14/H10</f>
+        <f t="shared" si="26"/>
         <v>0.23265564469389621</v>
       </c>
       <c r="I29" s="24">
-        <f>I14/I10</f>
+        <f t="shared" si="26"/>
         <v>0.31046676134886558</v>
       </c>
       <c r="J29" s="24" t="e">
-        <f>J14/J10</f>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K29" s="24">
-        <f>K14/K10</f>
+        <f t="shared" si="26"/>
         <v>0.17136390686525563</v>
       </c>
       <c r="L29" s="24">
-        <f>L14/L10</f>
+        <f t="shared" si="26"/>
         <v>0.2282023147242179</v>
       </c>
       <c r="M29" s="24"/>
       <c r="N29" s="24"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="24" t="e">
-        <f>P14/P10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q29" s="24" t="e">
-        <f>Q14/Q10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R29" s="24" t="e">
-        <f>R14/R10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S29" s="24">
-        <f>S14/S10</f>
+      <c r="O29" s="24"/>
+      <c r="P29" s="24"/>
+      <c r="Q29" s="24"/>
+      <c r="R29" s="24"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="24" t="e">
+        <f t="shared" ref="T29:AA29" si="27">T14/T10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U29" s="24" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V29" s="24" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W29" s="24">
+        <f t="shared" si="27"/>
         <v>0.17925277247940616</v>
       </c>
-      <c r="T29" s="24">
-        <f>T14/T10</f>
+      <c r="X29" s="24">
+        <f t="shared" si="27"/>
         <v>0.17995575755537341</v>
       </c>
-      <c r="U29" s="24">
-        <f>U14/U10</f>
+      <c r="Y29" s="24">
+        <f t="shared" si="27"/>
         <v>0.21632282381279003</v>
       </c>
-      <c r="V29" s="24">
-        <f>V14/V10</f>
+      <c r="Z29" s="24">
+        <f t="shared" si="27"/>
         <v>0.2364989493767265</v>
       </c>
-      <c r="W29" s="24">
-        <f>W14/W10</f>
+      <c r="AA29" s="24">
+        <f t="shared" si="27"/>
         <v>0.23078119312259424</v>
       </c>
     </row>
-    <row r="30" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C30" s="24" t="e">
-        <f>C20/C10</f>
+        <f t="shared" ref="C30:L30" si="28">C20/C10</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D30" s="24">
-        <f>D20/D10</f>
+        <f t="shared" si="28"/>
         <v>0.16351850478108487</v>
       </c>
       <c r="E30" s="24">
-        <f>E20/E10</f>
+        <f t="shared" si="28"/>
         <v>0.24989889810146332</v>
       </c>
       <c r="F30" s="24" t="e">
-        <f>F20/F10</f>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G30" s="24">
-        <f>G20/G10</f>
+        <f t="shared" si="28"/>
         <v>0.14009259135854377</v>
       </c>
       <c r="H30" s="24">
-        <f>H20/H10</f>
+        <f t="shared" si="28"/>
         <v>0.18479166031174693</v>
       </c>
       <c r="I30" s="24">
-        <f>I20/I10</f>
+        <f t="shared" si="28"/>
         <v>0.24996866730700296</v>
       </c>
       <c r="J30" s="24" t="e">
-        <f>J20/J10</f>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K30" s="24">
-        <f>K20/K10</f>
+        <f t="shared" si="28"/>
         <v>0.14432090804094802</v>
       </c>
       <c r="L30" s="24">
-        <f>L20/L10</f>
+        <f t="shared" si="28"/>
         <v>0.18740879483380385</v>
       </c>
       <c r="M30" s="24"/>
       <c r="N30" s="24"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="24" t="e">
-        <f>P20/P10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q30" s="24" t="e">
-        <f>Q20/Q10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R30" s="24" t="e">
-        <f>R20/R10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S30" s="24">
-        <f>S20/S10</f>
+      <c r="O30" s="24"/>
+      <c r="P30" s="24"/>
+      <c r="Q30" s="24"/>
+      <c r="R30" s="24"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="24" t="e">
+        <f t="shared" ref="T30:AA30" si="29">T20/T10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U30" s="24" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V30" s="24" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W30" s="24">
+        <f t="shared" si="29"/>
         <v>0.14346043394060129</v>
       </c>
-      <c r="T30" s="24">
-        <f>T20/T10</f>
+      <c r="X30" s="24">
+        <f t="shared" si="29"/>
         <v>0.14248173427736335</v>
       </c>
-      <c r="U30" s="24">
-        <f>U20/U10</f>
+      <c r="Y30" s="24">
+        <f t="shared" si="29"/>
         <v>0.17713199167024857</v>
       </c>
-      <c r="V30" s="24">
-        <f>V20/V10</f>
+      <c r="Z30" s="24">
+        <f t="shared" si="29"/>
         <v>0.19377580926875174</v>
       </c>
-      <c r="W30" s="24">
-        <f>W20/W10</f>
+      <c r="AA30" s="24">
+        <f t="shared" si="29"/>
         <v>0.18713735514306973</v>
       </c>
     </row>
-    <row r="31" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C31" s="24" t="e">
-        <f>C19/C18</f>
+        <f t="shared" ref="C31:L31" si="30">C19/C18</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D31" s="24">
-        <f>D19/D18</f>
+        <f t="shared" si="30"/>
         <v>0.23801089976399492</v>
       </c>
       <c r="E31" s="24">
-        <f>E19/E18</f>
+        <f t="shared" si="30"/>
         <v>0.21868218405660322</v>
       </c>
       <c r="F31" s="24" t="e">
-        <f>F19/F18</f>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G31" s="24">
-        <f>G19/G18</f>
+        <f t="shared" si="30"/>
         <v>0.22478931030552515</v>
       </c>
       <c r="H31" s="24">
-        <f>H19/H18</f>
+        <f t="shared" si="30"/>
         <v>0.24016343066425846</v>
       </c>
       <c r="I31" s="24">
-        <f>I19/I18</f>
+        <f t="shared" si="30"/>
         <v>0.21784355295560176</v>
       </c>
       <c r="J31" s="24" t="e">
-        <f>J19/J18</f>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K31" s="24">
-        <f>K19/K18</f>
+        <f t="shared" si="30"/>
         <v>0.23960211071416876</v>
       </c>
       <c r="L31" s="24">
-        <f>L19/L18</f>
+        <f t="shared" si="30"/>
         <v>0.2167451424832631</v>
       </c>
       <c r="M31" s="24"/>
       <c r="N31" s="24"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="24" t="e">
-        <f>P19/P18</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q31" s="24" t="e">
-        <f>Q19/Q18</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R31" s="24" t="e">
-        <f>R19/R18</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S31" s="24">
-        <f>S19/S18</f>
+      <c r="O31" s="24"/>
+      <c r="P31" s="24"/>
+      <c r="Q31" s="24"/>
+      <c r="R31" s="24"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="24" t="e">
+        <f t="shared" ref="T31:AA31" si="31">T19/T18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U31" s="24" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V31" s="24" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W31" s="24">
+        <f t="shared" si="31"/>
         <v>0.19957742837003534</v>
       </c>
-      <c r="T31" s="24">
-        <f>T19/T18</f>
+      <c r="X31" s="24">
+        <f t="shared" si="31"/>
         <v>0.22408652388144393</v>
       </c>
-      <c r="U31" s="24">
-        <f>U19/U18</f>
+      <c r="Y31" s="24">
+        <f t="shared" si="31"/>
         <v>0.22411168705395362</v>
       </c>
-      <c r="V31" s="24">
-        <f>V19/V18</f>
+      <c r="Z31" s="24">
+        <f t="shared" si="31"/>
         <v>0.22296165282848296</v>
       </c>
-      <c r="W31" s="24">
-        <f>W19/W18</f>
+      <c r="AA31" s="24">
+        <f t="shared" si="31"/>
         <v>0.22790638410803737</v>
       </c>
     </row>
-    <row r="32" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -2714,8 +2849,12 @@
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
-    </row>
-    <row r="33" spans="2:23" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+      <c r="Y32" s="3"/>
+    </row>
+    <row r="33" spans="2:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -2735,608 +2874,612 @@
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="V33" s="3"/>
+      <c r="W33" s="3"/>
+      <c r="X33" s="3"/>
+      <c r="Y33" s="3"/>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="T34" s="19">
+      <c r="X34" s="19">
         <v>981.79499999999996</v>
       </c>
-      <c r="U34" s="19">
+      <c r="Y34" s="19">
         <v>1502.0509999999999</v>
       </c>
-      <c r="V34" s="19">
+      <c r="Z34" s="19">
         <v>1889.1880000000001</v>
       </c>
-      <c r="W34" s="19">
+      <c r="AA34" s="19">
         <v>1907.249</v>
       </c>
     </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="T35" s="19">
+      <c r="X35" s="19">
         <v>301.51100000000002</v>
       </c>
-      <c r="U35" s="19">
+      <c r="Y35" s="19">
         <v>296.565</v>
       </c>
-      <c r="V35" s="19">
+      <c r="Z35" s="19">
         <v>332.87200000000001</v>
       </c>
-      <c r="W35" s="19">
+      <c r="AA35" s="19">
         <v>318.97800000000001</v>
       </c>
     </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="T36" s="19">
+      <c r="X36" s="19">
         <v>532.85199999999998</v>
       </c>
-      <c r="U36" s="19">
+      <c r="Y36" s="19">
         <v>474.31099999999998</v>
       </c>
-      <c r="V36" s="19">
+      <c r="Z36" s="19">
         <v>495.226</v>
       </c>
-      <c r="W36" s="19">
+      <c r="AA36" s="19">
         <v>487.01799999999997</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="T37" s="19">
+      <c r="X37" s="19">
         <v>33.787999999999997</v>
       </c>
-      <c r="U37" s="19">
+      <c r="Y37" s="19">
         <v>34.283999999999999</v>
       </c>
-      <c r="V37" s="19">
+      <c r="Z37" s="19">
         <v>39.293999999999997</v>
       </c>
-      <c r="W37" s="19">
+      <c r="AA37" s="19">
         <v>53.235999999999997</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="T38" s="19">
+      <c r="X38" s="19">
         <v>55.523000000000003</v>
       </c>
-      <c r="U38" s="19">
+      <c r="Y38" s="19">
         <v>92.712999999999994</v>
       </c>
-      <c r="V38" s="19">
+      <c r="Z38" s="19">
         <v>67.281999999999996</v>
       </c>
-      <c r="W38" s="19">
+      <c r="AA38" s="19">
         <v>82.114000000000004</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="T39" s="19">
+      <c r="X39" s="19">
         <v>4.7839999999999998</v>
       </c>
-      <c r="U39" s="19">
+      <c r="Y39" s="19">
         <v>43.558999999999997</v>
       </c>
-      <c r="V39" s="19">
+      <c r="Z39" s="19">
         <v>36.613</v>
       </c>
-      <c r="W39" s="19">
+      <c r="AA39" s="19">
         <v>1.825</v>
       </c>
     </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="P40" s="19">
-        <f t="shared" ref="P40:T40" si="20">SUM(P34:P39)</f>
-        <v>0</v>
-      </c>
-      <c r="Q40" s="19">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="R40" s="19">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="S40" s="19">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
       <c r="T40" s="19">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="T40:X40" si="32">SUM(T34:T39)</f>
+        <v>0</v>
+      </c>
+      <c r="U40" s="19">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="19">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="19">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="19">
+        <f t="shared" si="32"/>
         <v>1910.2529999999999</v>
       </c>
-      <c r="U40" s="19">
-        <f>SUM(U34:U39)</f>
+      <c r="Y40" s="19">
+        <f>SUM(Y34:Y39)</f>
         <v>2443.4830000000006</v>
       </c>
-      <c r="V40" s="19">
-        <f t="shared" ref="V40:W40" si="21">SUM(V34:V39)</f>
+      <c r="Z40" s="19">
+        <f t="shared" ref="Z40:AA40" si="33">SUM(Z34:Z39)</f>
         <v>2860.4749999999999</v>
       </c>
-      <c r="W40" s="19">
-        <f t="shared" si="21"/>
+      <c r="AA40" s="19">
+        <f t="shared" si="33"/>
         <v>2850.4199999999996</v>
       </c>
     </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="T41" s="19">
+      <c r="X41" s="19">
         <v>266.67899999999997</v>
       </c>
-      <c r="U41" s="19">
+      <c r="Y41" s="19">
         <v>302.12200000000001</v>
       </c>
-      <c r="V41" s="19">
+      <c r="Z41" s="19">
         <v>325.59899999999999</v>
       </c>
-      <c r="W41" s="19">
+      <c r="AA41" s="19">
         <v>337.78199999999998</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="T42" s="19">
+      <c r="X42" s="19">
         <v>213.30199999999999</v>
       </c>
-      <c r="U42" s="19">
+      <c r="Y42" s="19">
         <v>225.66900000000001</v>
       </c>
-      <c r="V42" s="19">
+      <c r="Z42" s="19">
         <v>237.352</v>
       </c>
-      <c r="W42" s="19">
+      <c r="AA42" s="19">
         <v>335.09800000000001</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="T43" s="19">
+      <c r="X43" s="19">
         <v>13.99</v>
       </c>
-      <c r="U43" s="19">
+      <c r="Y43" s="19">
         <v>13.99</v>
       </c>
-      <c r="V43" s="19">
+      <c r="Z43" s="19">
         <v>13.99</v>
       </c>
-      <c r="W43" s="19">
+      <c r="AA43" s="19">
         <v>13.99</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="T44" s="19">
+      <c r="X44" s="19">
         <v>37.457000000000001</v>
       </c>
-      <c r="U44" s="19">
+      <c r="Y44" s="19">
         <v>27.082999999999998</v>
       </c>
-      <c r="V44" s="19">
+      <c r="Z44" s="19">
         <v>15.699</v>
       </c>
-      <c r="W44" s="19">
+      <c r="AA44" s="19">
         <v>15.643000000000001</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T45" s="19">
+      <c r="X45" s="19">
         <v>72.591999999999999</v>
       </c>
-      <c r="U45" s="19">
+      <c r="Y45" s="19">
         <v>72.584000000000003</v>
       </c>
-      <c r="V45" s="19">
+      <c r="Z45" s="19">
         <v>77.590999999999994</v>
       </c>
-      <c r="W45" s="19">
+      <c r="AA45" s="19">
         <v>68.501000000000005</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="T46" s="19">
+      <c r="X46" s="19">
         <v>41.93</v>
       </c>
-      <c r="U46" s="19">
+      <c r="Y46" s="19">
         <v>50.648000000000003</v>
       </c>
-      <c r="V46" s="19">
+      <c r="Z46" s="19">
         <v>39.545999999999999</v>
       </c>
-      <c r="W46" s="19">
+      <c r="AA46" s="19">
         <v>66.331000000000003</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="P47" s="22">
-        <f t="shared" ref="P47:T47" si="22">SUM(P41:P46)+P40</f>
-        <v>0</v>
-      </c>
-      <c r="Q47" s="22">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="R47" s="22">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="S47" s="22">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
       <c r="T47" s="22">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="T47:X47" si="34">SUM(T41:T46)+T40</f>
+        <v>0</v>
+      </c>
+      <c r="U47" s="22">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="22">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="22">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="22">
+        <f t="shared" si="34"/>
         <v>2556.203</v>
       </c>
-      <c r="U47" s="22">
-        <f>SUM(U41:U46)+U40</f>
+      <c r="Y47" s="22">
+        <f>SUM(Y41:Y46)+Y40</f>
         <v>3135.5790000000006</v>
       </c>
-      <c r="V47" s="22">
-        <f t="shared" ref="V47:W47" si="23">SUM(V41:V46)+V40</f>
+      <c r="Z47" s="22">
+        <f t="shared" ref="Z47:AA47" si="35">SUM(Z41:Z46)+Z40</f>
         <v>3570.252</v>
       </c>
-      <c r="W47" s="22">
-        <f t="shared" si="23"/>
+      <c r="AA47" s="22">
+        <f t="shared" si="35"/>
         <v>3687.7649999999994</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="T48" s="19">
+      <c r="X48" s="19">
         <v>265.60500000000002</v>
       </c>
-      <c r="U48" s="19">
+      <c r="Y48" s="19">
         <v>378.50299999999999</v>
       </c>
-      <c r="V48" s="19">
+      <c r="Z48" s="19">
         <v>417.95499999999998</v>
       </c>
-      <c r="W48" s="19">
+      <c r="AA48" s="19">
         <v>384.529</v>
       </c>
     </row>
-    <row r="49" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="T49" s="19">
+      <c r="X49" s="19">
         <v>63.780999999999999</v>
       </c>
-      <c r="U49" s="19">
+      <c r="Y49" s="19">
         <v>123.65300000000001</v>
       </c>
-      <c r="V49" s="19">
+      <c r="Z49" s="19">
         <v>125.417</v>
       </c>
-      <c r="W49" s="19">
+      <c r="AA49" s="19">
         <v>119.59699999999999</v>
       </c>
     </row>
-    <row r="50" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="T50" s="19">
+      <c r="X50" s="19">
         <v>50.765000000000001</v>
       </c>
-      <c r="U50" s="19">
+      <c r="Y50" s="19">
         <v>53.581000000000003</v>
       </c>
-      <c r="V50" s="19">
+      <c r="Z50" s="19">
         <v>54.453000000000003</v>
       </c>
-      <c r="W50" s="19">
+      <c r="AA50" s="19">
         <v>83.930999999999997</v>
       </c>
     </row>
-    <row r="51" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="T51" s="19">
+      <c r="X51" s="19">
         <v>86.753</v>
       </c>
-      <c r="U51" s="19">
+      <c r="Y51" s="19">
         <v>106.785</v>
       </c>
-      <c r="V51" s="19">
+      <c r="Z51" s="19">
         <v>142.12</v>
       </c>
-      <c r="W51" s="19">
+      <c r="AA51" s="19">
         <v>171.173</v>
       </c>
     </row>
-    <row r="52" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="T52" s="19">
+      <c r="X52" s="19">
         <v>17.321999999999999</v>
       </c>
-      <c r="U52" s="19">
+      <c r="Y52" s="19">
         <v>52.338000000000001</v>
       </c>
-      <c r="V52" s="19">
+      <c r="Z52" s="19">
         <v>23.298999999999999</v>
       </c>
-      <c r="W52" s="19">
+      <c r="AA52" s="19">
         <v>36.475000000000001</v>
       </c>
     </row>
-    <row r="53" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="T53" s="19">
+      <c r="X53" s="19">
         <v>13.154</v>
       </c>
-      <c r="U53" s="19">
+      <c r="Y53" s="19">
         <v>5.133</v>
       </c>
-      <c r="V53" s="19">
+      <c r="Z53" s="19">
         <v>6.6970000000000001</v>
       </c>
-      <c r="W53" s="19">
+      <c r="AA53" s="19">
         <v>8.3689999999999998</v>
       </c>
     </row>
-    <row r="54" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="P54" s="19">
-        <f t="shared" ref="P54:T54" si="24">SUM(P48:P53)</f>
-        <v>0</v>
-      </c>
-      <c r="Q54" s="19">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="R54" s="19">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="S54" s="19">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
       <c r="T54" s="19">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="T54:X54" si="36">SUM(T48:T53)</f>
+        <v>0</v>
+      </c>
+      <c r="U54" s="19">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="19">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="19">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="X54" s="19">
+        <f t="shared" si="36"/>
         <v>497.38</v>
       </c>
-      <c r="U54" s="19">
-        <f>SUM(U48:U53)</f>
+      <c r="Y54" s="19">
+        <f>SUM(Y48:Y53)</f>
         <v>719.99299999999994</v>
       </c>
-      <c r="V54" s="19">
-        <f t="shared" ref="V54:W54" si="25">SUM(V48:V53)</f>
+      <c r="Z54" s="19">
+        <f t="shared" ref="Z54:AA54" si="37">SUM(Z48:Z53)</f>
         <v>769.94099999999992</v>
       </c>
-      <c r="W54" s="19">
-        <f t="shared" si="25"/>
+      <c r="AA54" s="19">
+        <f t="shared" si="37"/>
         <v>804.07400000000007</v>
       </c>
     </row>
-    <row r="55" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B55" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="T55" s="19">
+      <c r="X55" s="19">
         <v>195.72300000000001</v>
       </c>
-      <c r="U55" s="19">
+      <c r="Y55" s="19">
         <v>213.298</v>
       </c>
-      <c r="V55" s="19">
+      <c r="Z55" s="19">
         <v>222.52199999999999</v>
       </c>
-      <c r="W55" s="19">
+      <c r="AA55" s="19">
         <v>291.26299999999998</v>
       </c>
     </row>
-    <row r="56" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="T56" s="19">
+      <c r="X56" s="19">
         <v>62.031999999999996</v>
       </c>
-      <c r="U56" s="19">
+      <c r="Y56" s="19">
         <v>52.47</v>
       </c>
-      <c r="V56" s="19">
+      <c r="Z56" s="19">
         <v>13.587</v>
       </c>
-      <c r="W56" s="19">
+      <c r="AA56" s="19">
         <v>26.312999999999999</v>
       </c>
     </row>
-    <row r="57" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="T57" s="19">
+      <c r="X57" s="19">
         <v>35.335000000000001</v>
       </c>
-      <c r="U57" s="19">
+      <c r="Y57" s="19">
         <v>42.35</v>
       </c>
-      <c r="V57" s="19">
+      <c r="Z57" s="19">
         <v>51.189</v>
       </c>
-      <c r="W57" s="19">
+      <c r="AA57" s="19">
         <v>66.477000000000004</v>
       </c>
     </row>
-    <row r="58" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="P58" s="22">
-        <f t="shared" ref="P58:T58" si="26">SUM(P55:P57)+P54</f>
-        <v>0</v>
-      </c>
-      <c r="Q58" s="22">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="R58" s="22">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="S58" s="22">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
       <c r="T58" s="22">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="T58:X58" si="38">SUM(T55:T57)+T54</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="22">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V58" s="22">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="W58" s="22">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="X58" s="22">
+        <f t="shared" si="38"/>
         <v>790.47</v>
       </c>
-      <c r="U58" s="22">
-        <f>SUM(U55:U57)+U54</f>
+      <c r="Y58" s="22">
+        <f>SUM(Y55:Y57)+Y54</f>
         <v>1028.1109999999999</v>
       </c>
-      <c r="V58" s="22">
-        <f t="shared" ref="V58:W58" si="27">SUM(V55:V57)+V54</f>
+      <c r="Z58" s="22">
+        <f t="shared" ref="Z58:AA58" si="39">SUM(Z55:Z57)+Z54</f>
         <v>1057.239</v>
       </c>
-      <c r="W58" s="22">
-        <f t="shared" si="27"/>
+      <c r="AA58" s="22">
+        <f t="shared" si="39"/>
         <v>1188.127</v>
       </c>
     </row>
-    <row r="59" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B59" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="P59" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="19">
-        <v>0</v>
-      </c>
-      <c r="R59" s="19">
-        <v>0</v>
-      </c>
-      <c r="S59" s="19">
-        <v>0</v>
-      </c>
       <c r="T59" s="19">
+        <v>0</v>
+      </c>
+      <c r="U59" s="19">
+        <v>0</v>
+      </c>
+      <c r="V59" s="19">
+        <v>0</v>
+      </c>
+      <c r="W59" s="19">
+        <v>0</v>
+      </c>
+      <c r="X59" s="19">
         <v>1765.7339999999999</v>
       </c>
-      <c r="U59" s="19">
+      <c r="Y59" s="19">
         <v>2107.4679999999998</v>
       </c>
-      <c r="V59" s="19">
+      <c r="Z59" s="19">
         <v>2513.0129999999999</v>
       </c>
-      <c r="W59" s="19">
+      <c r="AA59" s="19">
         <v>2499.6379999999999</v>
       </c>
     </row>
-    <row r="60" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="P60" s="22">
-        <f>P59+P58</f>
-        <v>0</v>
-      </c>
-      <c r="Q60" s="22">
-        <f>Q59+Q58</f>
-        <v>0</v>
-      </c>
-      <c r="R60" s="22">
-        <f>R59+R58</f>
-        <v>0</v>
-      </c>
-      <c r="S60" s="22">
-        <f>S59+S58</f>
-        <v>0</v>
-      </c>
       <c r="T60" s="22">
-        <f>T59+T58</f>
+        <f t="shared" ref="T60:Y60" si="40">T59+T58</f>
+        <v>0</v>
+      </c>
+      <c r="U60" s="22">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="V60" s="22">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="W60" s="22">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="X60" s="22">
+        <f t="shared" si="40"/>
         <v>2556.2039999999997</v>
       </c>
-      <c r="U60" s="22">
-        <f>U59+U58</f>
+      <c r="Y60" s="22">
+        <f t="shared" si="40"/>
         <v>3135.5789999999997</v>
       </c>
-      <c r="V60" s="22">
-        <f t="shared" ref="V60:W60" si="28">V59+V58</f>
+      <c r="Z60" s="22">
+        <f t="shared" ref="Z60:AA60" si="41">Z59+Z58</f>
         <v>3570.252</v>
       </c>
-      <c r="W60" s="22">
-        <f t="shared" si="28"/>
+      <c r="AA60" s="22">
+        <f t="shared" si="41"/>
         <v>3687.7649999999999</v>
       </c>
     </row>
-    <row r="63" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B63" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="P63" s="19">
-        <f t="shared" ref="P63:T63" si="29">P18-P19</f>
-        <v>0</v>
-      </c>
-      <c r="Q63" s="19">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="R63" s="19">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="S63" s="19">
-        <f t="shared" si="29"/>
+      <c r="T63" s="19">
+        <f t="shared" ref="T63:X63" si="42">T18-T19</f>
+        <v>0</v>
+      </c>
+      <c r="U63" s="19">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V63" s="19">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="W63" s="19">
+        <f t="shared" si="42"/>
         <v>451.94899999999996</v>
       </c>
-      <c r="T63" s="19">
-        <f t="shared" si="29"/>
+      <c r="X63" s="19">
+        <f t="shared" si="42"/>
         <v>516.82200000000023</v>
       </c>
-      <c r="U63" s="19">
-        <f>U18-U19</f>
+      <c r="Y63" s="19">
+        <f>Y18-Y19</f>
         <v>759.5</v>
       </c>
     </row>
-    <row r="64" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B64" s="2" t="s">
         <v>88</v>
       </c>

--- a/DECK.xlsx
+++ b/DECK.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45EE06DD-7B76-4ECE-98C5-27509F02853B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FEAB85-CE60-4DF4-90C7-88898BDBD8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{32EF9E8E-5778-4FD9-8E72-014E2CEE3192}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{32EF9E8E-5778-4FD9-8E72-014E2CEE3192}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -379,13 +379,19 @@
     <numFmt numFmtId="166" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="167" formatCode="#,##0.00;[Red]#,##0.00"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -548,49 +554,50 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -963,7 +970,7 @@
         <v>4</v>
       </c>
       <c r="M3" s="3">
-        <v>138.26300000000001</v>
+        <v>136.41422700000001</v>
       </c>
       <c r="N3" s="28" t="s">
         <v>106</v>
@@ -984,7 +991,7 @@
       </c>
       <c r="M4" s="5">
         <f>M3*M2</f>
-        <v>14366.90833</v>
+        <v>14174.802327570002</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -1024,7 +1031,7 @@
       </c>
       <c r="M7" s="5">
         <f>M4-M5+M6</f>
-        <v>12764.31933</v>
+        <v>12572.213327570002</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -1228,8 +1235,14 @@
       <c r="H3" s="19">
         <v>512.40099999999995</v>
       </c>
+      <c r="K3" s="19">
+        <v>265.09199999999998</v>
+      </c>
       <c r="M3" s="19">
         <v>1305.4749999999999</v>
+      </c>
+      <c r="O3" s="19">
+        <v>278.04899999999998</v>
       </c>
       <c r="X3" s="19">
         <v>1929.211</v>
@@ -1255,8 +1268,14 @@
       <c r="H4" s="19">
         <v>362.34399999999999</v>
       </c>
+      <c r="K4" s="19">
+        <v>653.11900000000003</v>
+      </c>
       <c r="M4" s="19">
         <v>628.88199999999995</v>
+      </c>
+      <c r="O4" s="19">
+        <v>703.53800000000001</v>
       </c>
       <c r="X4" s="19">
         <v>1412.9159999999999</v>
@@ -1282,7 +1301,13 @@
       <c r="H5" s="19">
         <v>12.132</v>
       </c>
+      <c r="K5" s="19">
+        <v>0</v>
+      </c>
       <c r="M5" s="19">
+        <v>0</v>
+      </c>
+      <c r="O5" s="19">
         <v>0</v>
       </c>
       <c r="X5" s="19">
@@ -1309,7 +1334,13 @@
       <c r="H6" s="19">
         <v>1.895</v>
       </c>
+      <c r="K6" s="19">
+        <v>0</v>
+      </c>
       <c r="M6" s="19">
+        <v>0</v>
+      </c>
+      <c r="O6" s="19">
         <v>0</v>
       </c>
       <c r="X6" s="19">
@@ -1336,8 +1367,14 @@
       <c r="H7" s="19">
         <v>24.881</v>
       </c>
+      <c r="K7" s="19">
+        <v>-8.3829999999999991</v>
+      </c>
       <c r="M7" s="19">
         <v>23.192</v>
+      </c>
+      <c r="O7" s="30">
+        <v>37.944000000000003</v>
       </c>
       <c r="X7" s="19">
         <v>64.132000000000005</v>
@@ -1357,8 +1394,14 @@
       <c r="B8" s="3" t="s">
         <v>99</v>
       </c>
+      <c r="K8" s="19">
+        <v>652.36</v>
+      </c>
       <c r="M8" s="19">
         <v>864.57</v>
+      </c>
+      <c r="O8" s="19">
+        <v>666.71400000000006</v>
       </c>
       <c r="Z8" s="20">
         <v>2855.8649999999998</v>
@@ -1378,8 +1421,14 @@
       <c r="H9" s="19">
         <v>397.66699999999997</v>
       </c>
+      <c r="K9" s="19">
+        <v>312.17399999999998</v>
+      </c>
       <c r="M9" s="19">
         <v>1092.979</v>
+      </c>
+      <c r="O9" s="19">
+        <v>352.81700000000001</v>
       </c>
       <c r="Z9" s="20">
         <v>2129.7469999999998</v>
@@ -2318,40 +2367,52 @@
         <f t="shared" si="20"/>
         <v>-1</v>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
+      <c r="M25" s="24" t="e">
+        <f t="shared" ref="M25:M26" si="21">+M3/I3-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N25" s="24" t="e">
+        <f t="shared" ref="N25:N26" si="22">+N3/J3-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O25" s="24">
+        <f t="shared" ref="O25:O26" si="23">+O3/K3-1</f>
+        <v>4.8877370875016979E-2</v>
+      </c>
+      <c r="P25" s="24" t="e">
+        <f t="shared" ref="P25:P26" si="24">+P3/L3-1</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q25" s="24"/>
       <c r="R25" s="24"/>
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
       <c r="U25" s="24" t="e">
-        <f t="shared" ref="U25:AA26" si="21">U3/T3-1</f>
+        <f t="shared" ref="U25:AA26" si="25">U3/T3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V25" s="24" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W25" s="24" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X25" s="24" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y25" s="24">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0.16064650263760671</v>
       </c>
       <c r="Z25" s="24">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0.13050548158840125</v>
       </c>
       <c r="AA25" s="24">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>8.1935298581666371E-2</v>
       </c>
     </row>
@@ -2387,40 +2448,52 @@
         <f t="shared" si="20"/>
         <v>-1</v>
       </c>
-      <c r="M26" s="24"/>
-      <c r="N26" s="24"/>
-      <c r="O26" s="24"/>
-      <c r="P26" s="24"/>
+      <c r="M26" s="24" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N26" s="24" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O26" s="24">
+        <f t="shared" si="23"/>
+        <v>7.7197264204532434E-2</v>
+      </c>
+      <c r="P26" s="24" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q26" s="24"/>
       <c r="R26" s="24"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="24" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V26" s="24" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W26" s="24" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X26" s="24" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y26" s="24">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0.27873136124157427</v>
       </c>
       <c r="Z26" s="24">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0.2359775064480778</v>
       </c>
       <c r="AA26" s="24">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0.15863220918100018</v>
       </c>
     </row>
@@ -2433,63 +2506,75 @@
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
       <c r="G27" s="25" t="e">
-        <f t="shared" ref="G27:L27" si="22">+G10/C10-1</f>
+        <f t="shared" ref="G27:L27" si="26">+G10/C10-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H27" s="25">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0.20094476910579373</v>
       </c>
       <c r="I27" s="25">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0.17102916285064418</v>
       </c>
       <c r="J27" s="25" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K27" s="25">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0.16864543034626656</v>
       </c>
       <c r="L27" s="25">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>9.1144800658877978E-2</v>
       </c>
-      <c r="M27" s="25"/>
-      <c r="N27" s="25"/>
-      <c r="O27" s="25"/>
-      <c r="P27" s="25"/>
+      <c r="M27" s="25">
+        <f t="shared" ref="M27" si="27">+M10/I10-1</f>
+        <v>7.1358634824988387E-2</v>
+      </c>
+      <c r="N27" s="25" t="e">
+        <f t="shared" ref="N27" si="28">+N10/J10-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O27" s="25">
+        <f t="shared" ref="O27" si="29">+O10/K10-1</f>
+        <v>5.7014861000810768E-2</v>
+      </c>
+      <c r="P27" s="25">
+        <f t="shared" ref="P27" si="30">+P10/L10-1</f>
+        <v>-1</v>
+      </c>
       <c r="Q27" s="25"/>
       <c r="R27" s="25"/>
       <c r="S27" s="21"/>
       <c r="T27" s="21"/>
       <c r="U27" s="25" t="e">
-        <f t="shared" ref="U27:AA27" si="23">U10/T10-1</f>
+        <f t="shared" ref="U27:AA27" si="31">U10/T10-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V27" s="25" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W27" s="25" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X27" s="25">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>0.15139545299728074</v>
       </c>
       <c r="Y27" s="25">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>0.18208572469885187</v>
       </c>
       <c r="Z27" s="25">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>0.16275363167227308</v>
       </c>
       <c r="AA27" s="25">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>9.7617704707064989E-2</v>
       </c>
     </row>
@@ -2498,82 +2583,94 @@
         <v>51</v>
       </c>
       <c r="C28" s="24" t="e">
-        <f t="shared" ref="C28:L28" si="24">C12/C10</f>
+        <f t="shared" ref="C28:L28" si="32">C12/C10</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>0.53394565654400972</v>
       </c>
       <c r="E28" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>0.58742862782772876</v>
       </c>
       <c r="F28" s="24" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G28" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>0.56945745244121559</v>
       </c>
       <c r="H28" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>0.55918616356038187</v>
       </c>
       <c r="I28" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>0.60346109957228822</v>
       </c>
       <c r="J28" s="24" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K28" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>0.55768253816853242</v>
       </c>
       <c r="L28" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>0.56178328813843614</v>
       </c>
-      <c r="M28" s="24"/>
-      <c r="N28" s="24"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="24"/>
+      <c r="M28" s="24">
+        <f t="shared" ref="M28:P28" si="33">M12/M10</f>
+        <v>0.5983809345257769</v>
+      </c>
+      <c r="N28" s="24" t="e">
+        <f t="shared" si="33"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O28" s="24">
+        <f t="shared" si="33"/>
+        <v>0.56414469005846812</v>
+      </c>
+      <c r="P28" s="24" t="e">
+        <f t="shared" si="33"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q28" s="24"/>
       <c r="R28" s="24"/>
       <c r="S28" s="3"/>
       <c r="T28" s="24" t="e">
-        <f t="shared" ref="T28:AA28" si="25">T12/T10</f>
+        <f t="shared" ref="T28:AA28" si="34">T12/T10</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U28" s="24" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V28" s="24" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W28" s="24">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>0.51027873508216104</v>
       </c>
       <c r="X28" s="24">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>0.50323299568878777</v>
       </c>
       <c r="Y28" s="24">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>0.55634791381893067</v>
       </c>
       <c r="Z28" s="24">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>0.57879814955515996</v>
       </c>
       <c r="AA28" s="24">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>0.57703859586542827</v>
       </c>
     </row>
@@ -2582,82 +2679,94 @@
         <v>52</v>
       </c>
       <c r="C29" s="24" t="e">
-        <f t="shared" ref="C29:L29" si="26">C14/C10</f>
+        <f t="shared" ref="C29:L29" si="35">C14/C10</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D29" s="24">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.20571074276472268</v>
       </c>
       <c r="E29" s="24">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.31269423260935186</v>
       </c>
       <c r="F29" s="24" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G29" s="24">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.16091050188587347</v>
       </c>
       <c r="H29" s="24">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.23265564469389621</v>
       </c>
       <c r="I29" s="24">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.31046676134886558</v>
       </c>
       <c r="J29" s="24" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K29" s="24">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.17136390686525563</v>
       </c>
       <c r="L29" s="24">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.2282023147242179</v>
       </c>
-      <c r="M29" s="24"/>
-      <c r="N29" s="24"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="24"/>
+      <c r="M29" s="24">
+        <f t="shared" ref="M29:P29" si="36">M14/M10</f>
+        <v>0.31384450657429269</v>
+      </c>
+      <c r="N29" s="24" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O29" s="24">
+        <f t="shared" si="36"/>
+        <v>0.15232592240942158</v>
+      </c>
+      <c r="P29" s="24" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q29" s="24"/>
       <c r="R29" s="24"/>
       <c r="S29" s="3"/>
       <c r="T29" s="24" t="e">
-        <f t="shared" ref="T29:AA29" si="27">T14/T10</f>
+        <f t="shared" ref="T29:AA29" si="37">T14/T10</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U29" s="24" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V29" s="24" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W29" s="24">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>0.17925277247940616</v>
       </c>
       <c r="X29" s="24">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>0.17995575755537341</v>
       </c>
       <c r="Y29" s="24">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>0.21632282381279003</v>
       </c>
       <c r="Z29" s="24">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>0.2364989493767265</v>
       </c>
       <c r="AA29" s="24">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>0.23078119312259424</v>
       </c>
     </row>
@@ -2666,82 +2775,94 @@
         <v>53</v>
       </c>
       <c r="C30" s="24" t="e">
-        <f t="shared" ref="C30:L30" si="28">C20/C10</f>
+        <f t="shared" ref="C30:L30" si="38">C20/C10</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D30" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>0.16351850478108487</v>
       </c>
       <c r="E30" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>0.24989889810146332</v>
       </c>
       <c r="F30" s="24" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G30" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>0.14009259135854377</v>
       </c>
       <c r="H30" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>0.18479166031174693</v>
       </c>
       <c r="I30" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>0.24996866730700296</v>
       </c>
       <c r="J30" s="24" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K30" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>0.14432090804094802</v>
       </c>
       <c r="L30" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>0.18740879483380385</v>
       </c>
-      <c r="M30" s="24"/>
-      <c r="N30" s="24"/>
-      <c r="O30" s="24"/>
-      <c r="P30" s="24"/>
+      <c r="M30" s="24">
+        <f t="shared" ref="M30:P30" si="39">M20/M10</f>
+        <v>0.24578848345558663</v>
+      </c>
+      <c r="N30" s="24" t="e">
+        <f t="shared" si="39"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O30" s="24">
+        <f t="shared" si="39"/>
+        <v>0.13070617764442669</v>
+      </c>
+      <c r="P30" s="24" t="e">
+        <f t="shared" si="39"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q30" s="24"/>
       <c r="R30" s="24"/>
       <c r="S30" s="3"/>
       <c r="T30" s="24" t="e">
-        <f t="shared" ref="T30:AA30" si="29">T20/T10</f>
+        <f t="shared" ref="T30:AA30" si="40">T20/T10</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U30" s="24" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V30" s="24" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W30" s="24">
-        <f t="shared" si="29"/>
+        <f t="shared" si="40"/>
         <v>0.14346043394060129</v>
       </c>
       <c r="X30" s="24">
-        <f t="shared" si="29"/>
+        <f t="shared" si="40"/>
         <v>0.14248173427736335</v>
       </c>
       <c r="Y30" s="24">
-        <f t="shared" si="29"/>
+        <f t="shared" si="40"/>
         <v>0.17713199167024857</v>
       </c>
       <c r="Z30" s="24">
-        <f t="shared" si="29"/>
+        <f t="shared" si="40"/>
         <v>0.19377580926875174</v>
       </c>
       <c r="AA30" s="24">
-        <f t="shared" si="29"/>
+        <f t="shared" si="40"/>
         <v>0.18713735514306973</v>
       </c>
     </row>
@@ -2750,82 +2871,94 @@
         <v>54</v>
       </c>
       <c r="C31" s="24" t="e">
-        <f t="shared" ref="C31:L31" si="30">C19/C18</f>
+        <f t="shared" ref="C31:L31" si="41">C19/C18</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D31" s="24">
-        <f t="shared" si="30"/>
+        <f t="shared" si="41"/>
         <v>0.23801089976399492</v>
       </c>
       <c r="E31" s="24">
-        <f t="shared" si="30"/>
+        <f t="shared" si="41"/>
         <v>0.21868218405660322</v>
       </c>
       <c r="F31" s="24" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G31" s="24">
-        <f t="shared" si="30"/>
+        <f t="shared" si="41"/>
         <v>0.22478931030552515</v>
       </c>
       <c r="H31" s="24">
-        <f t="shared" si="30"/>
+        <f t="shared" si="41"/>
         <v>0.24016343066425846</v>
       </c>
       <c r="I31" s="24">
-        <f t="shared" si="30"/>
+        <f t="shared" si="41"/>
         <v>0.21784355295560176</v>
       </c>
       <c r="J31" s="24" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K31" s="24">
-        <f t="shared" si="30"/>
+        <f t="shared" si="41"/>
         <v>0.23960211071416876</v>
       </c>
       <c r="L31" s="24">
-        <f t="shared" si="30"/>
+        <f t="shared" si="41"/>
         <v>0.2167451424832631</v>
       </c>
-      <c r="M31" s="24"/>
-      <c r="N31" s="24"/>
-      <c r="O31" s="24"/>
-      <c r="P31" s="24"/>
+      <c r="M31" s="24">
+        <f t="shared" ref="M31:P31" si="42">M19/M18</f>
+        <v>0.23251785341140921</v>
+      </c>
+      <c r="N31" s="24" t="e">
+        <f t="shared" si="42"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O31" s="24">
+        <f t="shared" si="42"/>
+        <v>0.21171842650103523</v>
+      </c>
+      <c r="P31" s="24" t="e">
+        <f t="shared" si="42"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q31" s="24"/>
       <c r="R31" s="24"/>
       <c r="S31" s="3"/>
       <c r="T31" s="24" t="e">
-        <f t="shared" ref="T31:AA31" si="31">T19/T18</f>
+        <f t="shared" ref="T31:AA31" si="43">T19/T18</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U31" s="24" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V31" s="24" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W31" s="24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>0.19957742837003534</v>
       </c>
       <c r="X31" s="24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>0.22408652388144393</v>
       </c>
       <c r="Y31" s="24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>0.22411168705395362</v>
       </c>
       <c r="Z31" s="24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>0.22296165282848296</v>
       </c>
       <c r="AA31" s="24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>0.22790638410803737</v>
       </c>
     </row>
@@ -2986,23 +3119,23 @@
         <v>67</v>
       </c>
       <c r="T40" s="19">
-        <f t="shared" ref="T40:X40" si="32">SUM(T34:T39)</f>
+        <f t="shared" ref="T40:X40" si="44">SUM(T34:T39)</f>
         <v>0</v>
       </c>
       <c r="U40" s="19">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="V40" s="19">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="W40" s="19">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="X40" s="19">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>1910.2529999999999</v>
       </c>
       <c r="Y40" s="19">
@@ -3010,11 +3143,11 @@
         <v>2443.4830000000006</v>
       </c>
       <c r="Z40" s="19">
-        <f t="shared" ref="Z40:AA40" si="33">SUM(Z34:Z39)</f>
+        <f t="shared" ref="Z40:AA40" si="45">SUM(Z34:Z39)</f>
         <v>2860.4749999999999</v>
       </c>
       <c r="AA40" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>2850.4199999999996</v>
       </c>
     </row>
@@ -3125,23 +3258,23 @@
         <v>75</v>
       </c>
       <c r="T47" s="22">
-        <f t="shared" ref="T47:X47" si="34">SUM(T41:T46)+T40</f>
+        <f t="shared" ref="T47:X47" si="46">SUM(T41:T46)+T40</f>
         <v>0</v>
       </c>
       <c r="U47" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="V47" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="W47" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="X47" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>2556.203</v>
       </c>
       <c r="Y47" s="22">
@@ -3149,11 +3282,11 @@
         <v>3135.5790000000006</v>
       </c>
       <c r="Z47" s="22">
-        <f t="shared" ref="Z47:AA47" si="35">SUM(Z41:Z46)+Z40</f>
+        <f t="shared" ref="Z47:AA47" si="47">SUM(Z41:Z46)+Z40</f>
         <v>3570.252</v>
       </c>
       <c r="AA47" s="22">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>3687.7649999999994</v>
       </c>
     </row>
@@ -3264,23 +3397,23 @@
         <v>82</v>
       </c>
       <c r="T54" s="19">
-        <f t="shared" ref="T54:X54" si="36">SUM(T48:T53)</f>
+        <f t="shared" ref="T54:X54" si="48">SUM(T48:T53)</f>
         <v>0</v>
       </c>
       <c r="U54" s="19">
-        <f t="shared" si="36"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="V54" s="19">
-        <f t="shared" si="36"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="W54" s="19">
-        <f t="shared" si="36"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="X54" s="19">
-        <f t="shared" si="36"/>
+        <f t="shared" si="48"/>
         <v>497.38</v>
       </c>
       <c r="Y54" s="19">
@@ -3288,11 +3421,11 @@
         <v>719.99299999999994</v>
       </c>
       <c r="Z54" s="19">
-        <f t="shared" ref="Z54:AA54" si="37">SUM(Z48:Z53)</f>
+        <f t="shared" ref="Z54:AA54" si="49">SUM(Z48:Z53)</f>
         <v>769.94099999999992</v>
       </c>
       <c r="AA54" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="49"/>
         <v>804.07400000000007</v>
       </c>
     </row>
@@ -3352,23 +3485,23 @@
         <v>85</v>
       </c>
       <c r="T58" s="22">
-        <f t="shared" ref="T58:X58" si="38">SUM(T55:T57)+T54</f>
+        <f t="shared" ref="T58:X58" si="50">SUM(T55:T57)+T54</f>
         <v>0</v>
       </c>
       <c r="U58" s="22">
-        <f t="shared" si="38"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="V58" s="22">
-        <f t="shared" si="38"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="W58" s="22">
-        <f t="shared" si="38"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="X58" s="22">
-        <f t="shared" si="38"/>
+        <f t="shared" si="50"/>
         <v>790.47</v>
       </c>
       <c r="Y58" s="22">
@@ -3376,11 +3509,11 @@
         <v>1028.1109999999999</v>
       </c>
       <c r="Z58" s="22">
-        <f t="shared" ref="Z58:AA58" si="39">SUM(Z55:Z57)+Z54</f>
+        <f t="shared" ref="Z58:AA58" si="51">SUM(Z55:Z57)+Z54</f>
         <v>1057.239</v>
       </c>
       <c r="AA58" s="22">
-        <f t="shared" si="39"/>
+        <f t="shared" si="51"/>
         <v>1188.127</v>
       </c>
     </row>
@@ -3418,35 +3551,35 @@
         <v>87</v>
       </c>
       <c r="T60" s="22">
-        <f t="shared" ref="T60:Y60" si="40">T59+T58</f>
+        <f t="shared" ref="T60:Y60" si="52">T59+T58</f>
         <v>0</v>
       </c>
       <c r="U60" s="22">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="V60" s="22">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="W60" s="22">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="X60" s="22">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>2556.2039999999997</v>
       </c>
       <c r="Y60" s="22">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>3135.5789999999997</v>
       </c>
       <c r="Z60" s="22">
-        <f t="shared" ref="Z60:AA60" si="41">Z59+Z58</f>
+        <f t="shared" ref="Z60:AA60" si="53">Z59+Z58</f>
         <v>3570.252</v>
       </c>
       <c r="AA60" s="22">
-        <f t="shared" si="41"/>
+        <f t="shared" si="53"/>
         <v>3687.7649999999999</v>
       </c>
     </row>
@@ -3455,23 +3588,23 @@
         <v>60</v>
       </c>
       <c r="T63" s="19">
-        <f t="shared" ref="T63:X63" si="42">T18-T19</f>
+        <f t="shared" ref="T63:X63" si="54">T18-T19</f>
         <v>0</v>
       </c>
       <c r="U63" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="V63" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="W63" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="54"/>
         <v>451.94899999999996</v>
       </c>
       <c r="X63" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="54"/>
         <v>516.82200000000023</v>
       </c>
       <c r="Y63" s="19">
